--- a/data/evaluation_results_7.xlsx
+++ b/data/evaluation_results_7.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -521,57 +515,100 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>To determine the most likely consequence for the student, let's break down the situation:
+1. **Understanding the policy**: The class has a uniform policy in place, which means that all students are required to wear the same attire.
+2. **Non-compliance**: The student is caught wearing a non-uniform, which means they are not adhering to the established policy.
+3. **Possible consequences**: Given that the policy is in place to maintain a sense of unity and equality among students, the most likely consequence for the student would be related to the policy itself.
+Considering these points, the most likely consequence for the student would be:
+* **Detention or warning**: The student may receive a detention or a warning from the teacher or school administration, depending on the severity of the infraction and the school's policies.
+* **Parent contact**: The student's parents or guardians may be contacted to discuss the incident and the student's understanding of the uniform policy.
+* **Repetition of the policy**: The student may be required to attend a meeting or presentation to review the uniform policy and understand the importance of adhering to it.
+It's unlikely that the student would face more severe consequences, such as suspension or expulsion, unless the non-compliance is part of a larger pattern of behavior or is related to a more serious issue.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:45:27.599633+00:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2.625022907000016</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down into subproblems:
 1. **Understanding the context**: The problem states that all students in a class are required to wear a uniform. This implies that there is a rule or policy in place that governs what students can and cannot wear.
 2. **Identifying the consequence**: The problem asks for the most likely consequence for a student who is caught wearing a non-uniform.
 3. **Analyzing possible consequences**: In a typical school setting, consequences for violating uniform policies might include:
-	* Verbal warning
-	* Detention
-	* Loss of privileges (e.g., extracurricular activities)
-	* Parent contact
-	* Detention or suspension
-4. **Determining the most likely consequence**: Considering the context and the typical consequences for violating uniform policies, the most likely consequence for a student who is caught wearing a non-uniform is likely to be a verbal warning or a detention. This is because the school wants to address the issue, but also wants to give the student a chance to correct their behavior and avoid more severe consequences.
-Therefore, the most likely consequence for a student who is caught wearing a non-uniform is a verbal warning or a detention.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:02:49.529608+00:00</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>2.356202536000183</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>2.39480492000007</v>
-      </c>
-      <c r="I2" s="2" t="n">
+	* Verbal warning or reminder
+	* Detention or time-out
+	* Loss of privileges (e.g., recess, extracurricular activities)
+	* Parent contact or meeting
+	* Detention or suspension (in more severe cases)
+4. **Determining the most likely consequence**: Considering the context and typical school policies, the most likely consequence for a student caught wearing a non-uniform would be a verbal warning or reminder. This is because schools often use verbal warnings as a first step in addressing uniform policy violations, especially for first-time offenders.
+5. **Combining the results**: Based on the analysis, the most likely consequence for a student caught wearing a non-uniform is a verbal warning or reminder.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:45:30.225188+00:00</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2.502324723999948</v>
+      </c>
+      <c r="H3" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="I3" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down into subproblems:
 1. **Understanding the context**: The problem states that all students in a class are required to wear a uniform. This implies that there is a rule or policy in place that governs what students can and cannot wear.
@@ -582,79 +619,25 @@
 	* Loss of privileges (e.g., recess, extracurricular activities)
 	* Parent contact or meeting
 	* Detention or suspension
-4. **Determining the most likely consequence**: Considering the context and possible consequences, the most likely consequence for a student who is caught wearing a non-uniform is likely to be a verbal warning or reminder. This is because the school is likely to want to address the issue informally before escalating to more severe consequences.
-Therefore, the most likely consequence for a student who is caught wearing a non-uniform is a verbal warning or reminder.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:02:51.924882+00:00</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>2.23649606999993</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>2.279588688000104</v>
-      </c>
-      <c r="I3" s="2" t="n">
+4. **Determining the most likely consequence**: Considering the context and typical school policies, the most likely consequence for a student caught wearing a non-uniform would be a verbal warning or reminder. This is because schools often use verbal warnings as a first step in addressing uniform policy violations, especially for first-time offenders.
+5. **Combining the results**: Based on the analysis, the most likely consequence for a student caught wearing a non-uniform is a verbal warning or reminder.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:45:32.727920+00:00</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2.510537789000011</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>244</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's break it down into subproblems:
-1. **Understanding the context**: The problem states that all students in a class are required to wear a uniform. This implies that there is a rule or policy in place that governs what students can and cannot wear.
-2. **Identifying the consequence**: The problem asks for the most likely consequence for a student who is caught wearing a non-uniform.
-3. **Analyzing possible consequences**: In a typical school setting, consequences for violating uniform policies might include:
-	* Verbal warning or reminder
-	* Detention or time-out
-	* Loss of privileges (e.g., recess, extracurricular activities)
-	* Parent contact or meeting
-	* Detention or suspension
-4. **Determining the most likely consequence**: Considering the context and typical school policies, the most likely consequence for a student caught wearing a non-uniform would be a verbal warning or reminder. This is because the school likely wants to address the issue informally before escalating to more severe consequences.
-5. **Combining the results**: Based on the analysis, the most likely consequence for a student caught wearing a non-uniform is a verbal warning or reminder.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:02:54.204950+00:00</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>2.212150300000076</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>2.247589337999898</v>
-      </c>
       <c r="I4" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>248</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>252</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -676,36 +659,34 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Let's break this problem down into smaller subproblems and solve each one.
-Subproblem 1: Let's represent the cost of the ball as x. Since the bat costs $1.00 more than the ball, the cost of the bat can be represented as x + $1.00.
-Subproblem 2: The total cost of the bat and the ball together is $1.10. We can set up an equation to represent this:
+Subproblem 1: Let's represent the cost of the ball as x.
+Subproblem 2: Since the bat costs $1.00 more than the ball, the cost of the bat can be represented as x + $1.00.
+Subproblem 3: The total cost of the bat and the ball together is $1.10. We can set up an equation to represent this:
 x + (x + $1.00) = $1.10
-Subproblem 3: Now, let's simplify the equation by combining like terms:
+Subproblem 4: Simplify the equation by combining like terms:
 2x + $1.00 = $1.10
-Subproblem 4: Subtract $1.00 from both sides of the equation to isolate the term with x:
+Subproblem 5: Subtract $1.00 from both sides of the equation to isolate the term with x:
 2x = $0.10
-Subproblem 5: Divide both sides of the equation by 2 to solve for x:
+Subproblem 6: Divide both sides of the equation by 2 to solve for x:
 x = $0.05
 Therefore, the ball costs $0.05.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:02:56.452896+00:00</t>
+          <t>2026-10-22T04:45:35.238738+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.990898397000137</v>
+        <v>2.188322577000008</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2.01270642999998</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -725,57 +706,6 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Let's break down the problem into subproblems and solve each one.
-Subproblem 1: Let's represent the cost of the ball as x. Since the bat costs $1.00 more than the ball, the cost of the bat can be represented as x + $1.00.
-Subproblem 2: The total cost of the bat and the ball together is $1.10. We can set up an equation to represent this:
-x + (x + $1.00) = $1.10
-Subproblem 3: Now, let's simplify the equation by combining like terms:
-2x + $1.00 = $1.10
-Subproblem 4: Subtract $1.00 from both sides of the equation to isolate the term with x:
-2x = $0.10
-Subproblem 5: Divide both sides of the equation by 2 to solve for x:
-x = $0.05
-Therefore, the ball costs $0.05.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:02:58.465901+00:00</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1.859421284000064</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1.882329062000053</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>204</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down into smaller subproblems.
 Let's say the cost of the ball is x.
@@ -791,24 +721,71 @@
 So, the ball costs $0.05.</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:45:37.427364+00:00</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1.502555120000011</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>A bat and a ball together cost $1.10. The bat costs $1.00 more than the ball. How much does the ball cost?</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>To solve this problem, let's break it down into smaller subproblems:
+1. Let's denote the cost of the ball as x.
+2. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
+3. The total cost of the bat and the ball together is $1.10, so we can set up the equation: x + (x + $1.00) = $1.10.
+Now, let's solve the equation:
+x + x + $1.00 = $1.10
+Combine like terms:
+2x + $1.00 = $1.10
+Subtract $1.00 from both sides:
+2x = $0.10
+Divide both sides by 2:
+x = $0.05
+So, the ball costs $0.05.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:03:00.348452+00:00</t>
+          <t>2026-10-22T04:45:38.930160+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.437990166999953</v>
+        <v>1.753831641000033</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.454559878000055</v>
+        <v>77</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>153</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -828,151 +805,153 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>To solve this problem, let's break it down into manageable subproblems.
+**Subproblem 1: Calculate the net progress of the snail per day**
+The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress per day is:
+Net progress per day = 3 feet (up) - 2 feet (down) = 1 foot
+**Subproblem 2: Calculate the number of days to reach the top of the well**
+The well is 20 feet deep. Since the snail makes a net progress of 1 foot per day, we can calculate the number of days it takes to reach the top:
+Number of days = Total depth / Net progress per day
+= 20 feet / 1 foot
+= 20 days
+However, this calculation assumes that the snail reaches the top on the 20th day, but it doesn't account for the fact that the snail will climb 3 feet on the 20th day and reach the top.
+**Subproblem 3: Adjust the calculation to account for the final climb**
+Since the snail climbs 3 feet on the 20th day and reaches the top, we need to adjust the calculation:
+Number of days = Total depth / Net progress per day
+= 20 feet / 1 foot
+= 20 days
+But we need to add 1 day to account for the final climb:
+Total number of days = 20 days + 1 day
+= 21 days
+Therefore, it will take the snail **21 days** to reach the top of the well.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:45:40.684228+00:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>3.541824496999993</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>336</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>To solve this problem, let's break it down into smaller subproblems.
+**Subproblem 1: Calculate the net progress of the snail per day**
+The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress per day is:
+Net progress per day = 3 feet (up) - 2 feet (down) = 1 foot
+**Subproblem 2: Calculate the total distance the snail needs to cover**
+The well is 20 feet deep, and the snail starts at the bottom. To reach the top, the snail needs to cover a distance of:
+Total distance = 20 feet
+**Subproblem 3: Calculate the number of days required to reach the top**
+Since the snail makes a net progress of 1 foot per day, we can divide the total distance by the net progress to find the number of days:
+Number of days = Total distance / Net progress per day
+= 20 feet / 1 foot
+= 20 days
+However, this calculation assumes that the snail will climb 3 feet up on the 20th day and reach the top. But, on the 20th day, the snail will only climb 3 feet, and then slip back 2 feet, so it will be 1 foot short of the top.
+**Subproblem 4: Add one more day to account for the final climb**
+Since the snail will be 1 foot short of the top on the 20th day, it will need one more day to climb the remaining 1 foot and reach the top.
+Therefore, the total number of days required for the snail to reach the top of the well is:
+Total number of days = 20 days + 1 day = 21 days
+The final answer is 21.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:45:44.226310+00:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>3.787763931000029</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down into smaller subproblems.
 **Subproblem 1: Calculate the net progress of the snail per day**
 The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress per day is:
 Net progress = 3 feet (up) - 2 feet (down) = 1 foot
-**Subproblem 2: Determine the number of days to reach the top**
-Since the snail starts at the bottom of the 20-foot well, we need to find out how many days it will take to cover the remaining distance.
-Let's assume it takes x days to reach the top. In those x days, the snail will climb 3x feet and slip back 2x feet.
-Since the snail climbs 1 foot net progress per day, we can set up the equation:
-3x - 2x = 20 (the remaining distance to the top)
-Simplifying the equation, we get:
-x = 20
-However, this is not the correct answer. The snail will climb 3 feet on the last day, so it will reach the top on the 20th day, but it will not slip back 2 feet on the 20th day. Therefore, we need to add 1 day to the total number of days.
-**Final answer**
-The snail will reach the top of the well in 18 days (since it climbs 3 feet on the 19th day and reaches the top on the 20th day).</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:01.803243+00:00</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>2.789965806999817</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>2.819257335999964</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>326</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's break it down into smaller subproblems.
-**Subproblem 1: Calculate the net progress of the snail per day**
-The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress per day is:
-Net progress = 3 feet (up) - 2 feet (down) = 1 foot
-**Subproblem 2: Determine the total distance to the top of the well**
+**Subproblem 2: Determine the total distance the snail needs to cover**
 The well is 20 feet deep, and the snail starts at the bottom. To reach the top, the snail needs to cover a distance of:
-Total distance = 20 feet
+20 feet (well depth) - 0 feet (initial position) = 20 feet
 **Subproblem 3: Calculate the number of days required to reach the top**
 Since the snail makes a net progress of 1 foot per day, we can divide the total distance by the net progress to find the number of days:
 Number of days = Total distance / Net progress
 = 20 feet / 1 foot
 = 20 days
-However, this calculation assumes that the snail will climb 3 feet up on the 20th day and reach the top. But, on the 20th day, the snail will only climb 1 foot (3 feet - 2 feet), and then it will slip back 2 feet, so it will be at 18 feet. On the 21st day, it will climb 3 feet and reach the top.
+However, this calculation assumes that the snail will climb 3 feet up on the 20th day and reach the top. But, on the 20th day, the snail will only climb 3 feet, and then slip back 2 feet, so it will be at 19 feet. On the 21st day, it will climb 3 feet and reach the top.
 Therefore, the correct answer is:
-The snail will take 21 days to reach the top of the well.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:04.622760+00:00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2.80390771500015</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2.832139217000076</v>
-      </c>
-      <c r="I9" s="2" t="n">
+**21 days**</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:45:48.014344+00:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2.711586604000047</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>325</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's break it down into smaller subproblems.
-**Subproblem 1: Calculate the net progress of the snail per day**
-The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress per day is:
-3 feet (up) - 2 feet (down) = 1 foot
-**Subproblem 2: Determine the total distance to the top of the well**
-The well is 20 feet deep, and the snail starts at the bottom. To reach the top, the snail needs to cover a distance of:
-20 feet (total depth) - 0 feet (initial position) = 20 feet
-**Subproblem 3: Calculate the number of days required to reach the top**
-Since the snail makes a net progress of 1 foot per day, we can divide the total distance by the net progress to find the number of days:
-20 feet (total distance) ÷ 1 foot (net progress) = 20 days
-However, this calculation assumes that the snail will climb exactly 3 feet up on the 20th day and reach the top. Since the snail climbs 3 feet up, but the well is only 20 feet deep, it will actually reach the top on the 18th day (20 - 3 = 17, but since it climbs 3 feet on the 18th day, it will reach the top).
-Therefore, the snail will take **18 days** to reach the top of the well.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:03:07.455154+00:00</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>2.781773359999988</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2.811697830999947</v>
-      </c>
       <c r="I10" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>324</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>316</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1044,10 +1023,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1072,16 +1051,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 2.7899658069998168,
-  "median_total_latency_seconds": 2.819257335999964,
-  "num_correct_answers": 3,
-  "num_total_answers": 6,
-  "accuracy": 0.5,
-  "mode": "median",
-  "metric_notes": {
-    "ttft_seconds": "Time to first nonempty streamed token, client-side.",
-    "total_latency_seconds": "Time between the start of the request and the receival of the answer."
-  }
+  "median_input": 80,
+  "median_output": 257,
+  "median_latency": 2.503,
+  "correct_frequency": 0.75,
+  "misinformation_frequency": 0,
+  "total_correct": 15
 }</t>
         </is>
       </c>
@@ -1089,79 +1064,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.789965806999817</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_total_latency_seconds</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.819257335999964</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>num_correct_answers</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3</v>
+        <v>2.503</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>num_total_answers</t>
+          <t>correct_frequency</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>misinformation_frequency</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>mode</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>metric_notes</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>{"ttft_seconds": "Time to first nonempty streamed token, client-side.", "total_latency_seconds": "Time between the start of the request and the receival of the answer."}</t>
-        </is>
+          <t>total_correct</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1199,7 +1160,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:03:12.481989+00:00</t>
+          <t>2026-10-22T04:45:52.404391+00:00</t>
         </is>
       </c>
     </row>
